--- a/Data/Export/Data/MediaData_音效.xlsx
+++ b/Data/Export/Data/MediaData_音效.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE0BD5-B3D6-4321-BA4F-39AA6E840C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDC55B0-39AF-4BCE-B7CE-A975B8928E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5610" yWindow="645" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1970,13 +1970,13 @@
       </c>
       <c r="C48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Assets/Sound/2264.mp3</v>
+        <v>Assets/Sound/2264.ogg</v>
       </c>
       <c r="D48" s="4">
         <v>2264</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>97</v>
@@ -1992,13 +1992,13 @@
       </c>
       <c r="C49" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Assets/Sound/2291.mp3</v>
+        <v>Assets/Sound/2291.ogg</v>
       </c>
       <c r="D49" s="4">
         <v>2291</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>98</v>
@@ -2266,13 +2266,13 @@
       </c>
       <c r="C61" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Assets/Sound/3286.mp3</v>
+        <v>Assets/Sound/3286.ogg</v>
       </c>
       <c r="D61" s="4">
         <v>3286</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>114</v>

--- a/Data/Export/Data/MediaData_音效.xlsx
+++ b/Data/Export/Data/MediaData_音效.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91647E4B-51E3-4A15-AEFA-9FC1FA72A43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897FE662-1F79-496D-A6FC-D124141A6419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MediaData" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="182">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -387,6 +387,222 @@
   <si>
     <t>伏兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮音</t>
+  </si>
+  <si>
+    <t>取消音</t>
+  </si>
+  <si>
+    <t>出现消息框音</t>
+  </si>
+  <si>
+    <t>过回合音_前</t>
+  </si>
+  <si>
+    <t>过回合_人物弹出窗口+开发耐久提升音</t>
+  </si>
+  <si>
+    <t>发生关系变化</t>
+  </si>
+  <si>
+    <t>授予官职</t>
+  </si>
+  <si>
+    <t>鸟叫声</t>
+  </si>
+  <si>
+    <t>交谈音</t>
+  </si>
+  <si>
+    <t>舌战失败</t>
+  </si>
+  <si>
+    <t>点击地面城池音</t>
+  </si>
+  <si>
+    <t>褒奖征兵巡查后音</t>
+  </si>
+  <si>
+    <t>开发设施音</t>
+  </si>
+  <si>
+    <t>军饷0</t>
+  </si>
+  <si>
+    <t>能力研发音</t>
+  </si>
+  <si>
+    <t>取消军团最后音效</t>
+  </si>
+  <si>
+    <t>修筑建筑</t>
+  </si>
+  <si>
+    <t>耐久上升</t>
+  </si>
+  <si>
+    <t>技巧点图标到左上角音效</t>
+  </si>
+  <si>
+    <t>技巧上升</t>
+  </si>
+  <si>
+    <t>船行声</t>
+  </si>
+  <si>
+    <t>冲车行进音</t>
+  </si>
+  <si>
+    <t>井阑行进音</t>
+  </si>
+  <si>
+    <t>弓兵发射</t>
+  </si>
+  <si>
+    <t>戟兵横扫预备</t>
+  </si>
+  <si>
+    <t>铜锣</t>
+  </si>
+  <si>
+    <t>左下角消息提示音</t>
+  </si>
+  <si>
+    <t>脚步声</t>
+  </si>
+  <si>
+    <t>卷轴声</t>
+  </si>
+  <si>
+    <t>起义声</t>
+  </si>
+  <si>
+    <t>去世</t>
+  </si>
+  <si>
+    <t>市集音</t>
+  </si>
+  <si>
+    <t>点击都市，开发，一并等按钮音</t>
+  </si>
+  <si>
+    <t>收获金钱</t>
+  </si>
+  <si>
+    <t>部队行军</t>
+  </si>
+  <si>
+    <t>集气</t>
+  </si>
+  <si>
+    <t>突刺音</t>
+  </si>
+  <si>
+    <t>突刺音2</t>
+  </si>
+  <si>
+    <t>弓兵集气</t>
+  </si>
+  <si>
+    <t>弓兵射中</t>
+  </si>
+  <si>
+    <t>骑兵突进</t>
+  </si>
+  <si>
+    <t>会心改普攻</t>
+  </si>
+  <si>
+    <t>带暴击图的集气</t>
+  </si>
+  <si>
+    <t>戟兵熊手预备</t>
+  </si>
+  <si>
+    <t>戟兵熊手成功</t>
+  </si>
+  <si>
+    <t>戟兵横扫成功</t>
+  </si>
+  <si>
+    <t>戟兵旋风成功</t>
+  </si>
+  <si>
+    <t>部队普通攻击</t>
+  </si>
+  <si>
+    <t>部队普通攻击2</t>
+  </si>
+  <si>
+    <t>部队溃灭</t>
+  </si>
+  <si>
+    <t>部队齐攻</t>
+  </si>
+  <si>
+    <t>使用计策预备</t>
+  </si>
+  <si>
+    <t>火焰声</t>
+  </si>
+  <si>
+    <t>计策灭火成功</t>
+  </si>
+  <si>
+    <t>计策伪报成功</t>
+  </si>
+  <si>
+    <t>计策扰乱成功</t>
+  </si>
+  <si>
+    <t>计策内讧成功</t>
+  </si>
+  <si>
+    <t>计策暴击预备</t>
+  </si>
+  <si>
+    <t>计策镇静成功</t>
+  </si>
+  <si>
+    <t>部队攻城</t>
+  </si>
+  <si>
+    <t>箭矢音</t>
+  </si>
+  <si>
+    <t>中箭音</t>
+  </si>
+  <si>
+    <t>冲车破碎</t>
+  </si>
+  <si>
+    <t>井阑战法音</t>
+  </si>
+  <si>
+    <t>木兽战法</t>
+  </si>
+  <si>
+    <t>投石发出</t>
+  </si>
+  <si>
+    <t>投石射中</t>
+  </si>
+  <si>
+    <t>设施完成</t>
+  </si>
+  <si>
+    <t>设施被摧毁</t>
+  </si>
+  <si>
+    <t>楼船二战法</t>
+  </si>
+  <si>
+    <t>楼船二战法攻城+船普通撞击</t>
+  </si>
+  <si>
+    <t>楼船二战法撞到两个船</t>
   </si>
 </sst>
 </file>
@@ -859,21 +1075,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:J450"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K450"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="45" style="2" customWidth="1"/>
-    <col min="4" max="4" width="42.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="51.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="65.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="100.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="42.08984375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="51.26953125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="65.90625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="39.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="100.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="8" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -883,7 +1099,7 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -891,7 +1107,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -903,7 +1119,7 @@
       </c>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:10" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -914,7 +1130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -928,13 +1144,13 @@
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -948,13 +1164,13 @@
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K6" s="11"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -968,13 +1184,13 @@
       <c r="E7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K7" s="11"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4">
         <v>4</v>
@@ -989,13 +1205,13 @@
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="4">
         <v>5</v>
@@ -1010,13 +1226,13 @@
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K9" s="11"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1030,13 +1246,13 @@
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1050,13 +1266,13 @@
       <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1070,13 +1286,13 @@
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K12" s="11"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1090,15 +1306,15 @@
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1112,15 +1328,15 @@
       <c r="E14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -1134,15 +1350,15 @@
       <c r="E15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="G15" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -1156,15 +1372,15 @@
       <c r="E16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -1178,15 +1394,15 @@
       <c r="E17" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -1200,15 +1416,15 @@
       <c r="E18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -1222,15 +1438,15 @@
       <c r="E19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="G19" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -1244,15 +1460,15 @@
       <c r="E20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -1266,15 +1482,15 @@
       <c r="E21" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -1288,15 +1504,15 @@
       <c r="E22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -1305,13 +1521,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D23" s="4"/>
-      <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -1320,13 +1536,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -1335,13 +1551,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
-    </row>
-    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -1350,13 +1566,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D26" s="4"/>
-      <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -1365,13 +1581,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D27" s="4"/>
-      <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -1380,13 +1596,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -1395,13 +1611,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D29" s="4"/>
-      <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -1410,13 +1626,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D30" s="4"/>
-      <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -1425,13 +1641,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D31" s="4"/>
-      <c r="F31" s="11"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -1440,13 +1656,13 @@
         <v>Assets/Sound/.</v>
       </c>
       <c r="D32" s="4"/>
-      <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -1460,15 +1676,15 @@
       <c r="E33" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="G33" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="11"/>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -1482,21 +1698,24 @@
       <c r="E34" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="H34" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="I34" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="J34" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -1510,17 +1729,20 @@
       <c r="E35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="H35" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>32</v>
       </c>
@@ -1534,15 +1756,18 @@
       <c r="E36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="4">
         <v>33</v>
@@ -1557,15 +1782,18 @@
       <c r="E37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="11"/>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="4">
         <v>34</v>
@@ -1580,15 +1808,18 @@
       <c r="E38" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="11"/>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K38" s="11"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -1602,15 +1833,18 @@
       <c r="E39" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="11"/>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>36</v>
       </c>
@@ -1624,15 +1858,18 @@
       <c r="E40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K40" s="11"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>37</v>
       </c>
@@ -1646,15 +1883,18 @@
       <c r="E41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="11"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K41" s="11"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>38</v>
       </c>
@@ -1668,15 +1908,18 @@
       <c r="E42" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K42" s="11"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -1690,15 +1933,18 @@
       <c r="E43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
       <c r="J43" s="11"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
         <v>40</v>
       </c>
@@ -1712,13 +1958,16 @@
       <c r="E44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F44" s="11"/>
+      <c r="F44" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K44" s="11"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -1732,13 +1981,16 @@
       <c r="E45" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="11"/>
+      <c r="F45" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K45" s="11"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" s="4">
         <v>42</v>
       </c>
@@ -1752,13 +2004,16 @@
       <c r="E46" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F46" s="11"/>
+      <c r="F46" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
-    </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K46" s="11"/>
+    </row>
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -1772,15 +2027,18 @@
       <c r="E47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="11"/>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K47" s="11"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -1794,15 +2052,18 @@
       <c r="E48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="2">
+        <v>2264</v>
+      </c>
+      <c r="G48" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G48" s="11"/>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K48" s="11"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -1816,15 +2077,18 @@
       <c r="E49" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="2">
+        <v>2291</v>
+      </c>
+      <c r="G49" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="11"/>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K49" s="11"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="4">
         <v>46</v>
       </c>
@@ -1838,15 +2102,18 @@
       <c r="E50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K50" s="11"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -1860,15 +2127,18 @@
       <c r="E51" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K51" s="11"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -1882,15 +2152,18 @@
       <c r="E52" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G52" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G52" s="11"/>
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K52" s="11"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -1904,17 +2177,20 @@
       <c r="E53" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="H53" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="11"/>
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K53" s="11"/>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -1928,23 +2204,26 @@
       <c r="E54" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="H54" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="I54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="J54" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="K54" s="11" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -1958,15 +2237,18 @@
       <c r="E55" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G55" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G55" s="11"/>
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
       <c r="J55" s="11"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -1980,15 +2262,18 @@
       <c r="E56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G56" s="11"/>
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -2002,15 +2287,18 @@
       <c r="E57" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G57" s="11"/>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K57" s="11"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -2024,15 +2312,18 @@
       <c r="E58" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G58" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G58" s="11"/>
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K58" s="11"/>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -2046,15 +2337,18 @@
       <c r="E59" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G59" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G59" s="11"/>
       <c r="H59" s="11"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K59" s="11"/>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -2068,15 +2362,18 @@
       <c r="E60" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G60" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G60" s="11"/>
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K60" s="11"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -2090,15 +2387,18 @@
       <c r="E61" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="2">
+        <v>3286</v>
+      </c>
+      <c r="G61" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
       <c r="J61" s="11"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K61" s="11"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -2112,15 +2412,18 @@
       <c r="E62" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G62" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G62" s="11"/>
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
       <c r="J62" s="11"/>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K62" s="11"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -2134,19 +2437,22 @@
       <c r="E63" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G63" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="H63" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="I63" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I63" s="11"/>
       <c r="J63" s="11"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K63" s="11"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -2160,15 +2466,18 @@
       <c r="E64" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G64" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G64" s="11"/>
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
       <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K64" s="11"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
         <v>61</v>
       </c>
@@ -2182,15 +2491,18 @@
       <c r="E65" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G65" s="11"/>
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K65" s="11"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
         <v>62</v>
       </c>
@@ -2204,15 +2516,18 @@
       <c r="E66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G66" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G66" s="11"/>
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K66" s="11"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
         <v>63</v>
       </c>
@@ -2226,15 +2541,18 @@
       <c r="E67" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G67" s="11"/>
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K67" s="11"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="4">
         <v>64</v>
       </c>
@@ -2248,15 +2566,18 @@
       <c r="E68" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G68" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G68" s="11"/>
       <c r="H68" s="11"/>
       <c r="I68" s="11"/>
       <c r="J68" s="11"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K68" s="11"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
         <v>65</v>
       </c>
@@ -2270,15 +2591,18 @@
       <c r="E69" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
       <c r="J69" s="11"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="4">
         <v>66</v>
       </c>
@@ -2292,17 +2616,20 @@
       <c r="E70" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G70" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="H70" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H70" s="11"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
         <v>67</v>
       </c>
@@ -2316,15 +2643,18 @@
       <c r="E71" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G71" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
       <c r="J71" s="11"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="4">
         <v>68</v>
       </c>
@@ -2338,15 +2668,18 @@
       <c r="E72" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G72" s="11"/>
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
       <c r="J72" s="11"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K72" s="11"/>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
         <v>69</v>
       </c>
@@ -2360,17 +2693,20 @@
       <c r="E73" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G73" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="H73" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H73" s="11"/>
       <c r="I73" s="11"/>
       <c r="J73" s="11"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K73" s="11"/>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="4">
         <v>70</v>
       </c>
@@ -2384,15 +2720,18 @@
       <c r="E74" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G74" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
       <c r="J74" s="11"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K74" s="11"/>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -2406,15 +2745,18 @@
       <c r="E75" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G75" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G75" s="11"/>
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
       <c r="J75" s="11"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K75" s="11"/>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -2428,15 +2770,18 @@
       <c r="E76" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="11"/>
+      <c r="G76" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
       <c r="J76" s="11"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K76" s="11"/>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
         <v>73</v>
       </c>
@@ -2450,15 +2795,18 @@
       <c r="E77" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G77" s="11"/>
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
       <c r="J77" s="11"/>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K77" s="11"/>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" s="4">
         <v>74</v>
       </c>
@@ -2472,15 +2820,18 @@
       <c r="E78" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G78" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G78" s="11"/>
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K78" s="11"/>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="4">
         <v>75</v>
       </c>
@@ -2494,15 +2845,18 @@
       <c r="E79" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G79" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G79" s="11"/>
       <c r="H79" s="11"/>
       <c r="I79" s="11"/>
       <c r="J79" s="11"/>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K79" s="11"/>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="4">
         <v>76</v>
       </c>
@@ -2516,15 +2870,18 @@
       <c r="E80" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G80" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G80" s="11"/>
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
       <c r="J80" s="11"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K80" s="11"/>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="4">
         <v>77</v>
       </c>
@@ -2538,15 +2895,18 @@
       <c r="E81" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G81" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
       <c r="J81" s="11"/>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K81" s="11"/>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="4">
         <v>78</v>
       </c>
@@ -2560,15 +2920,18 @@
       <c r="E82" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G82" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G82" s="11"/>
       <c r="H82" s="11"/>
       <c r="I82" s="11"/>
       <c r="J82" s="11"/>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K82" s="11"/>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" s="4">
         <v>79</v>
       </c>
@@ -2582,15 +2945,18 @@
       <c r="E83" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G83" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G83" s="11"/>
       <c r="H83" s="11"/>
       <c r="I83" s="11"/>
       <c r="J83" s="11"/>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K83" s="11"/>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" s="4">
         <v>80</v>
       </c>
@@ -2604,15 +2970,18 @@
       <c r="E84" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G84" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G84" s="11"/>
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
       <c r="J84" s="11"/>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K84" s="11"/>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" s="4">
         <v>81</v>
       </c>
@@ -2626,15 +2995,18 @@
       <c r="E85" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G85" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G85" s="11"/>
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
       <c r="J85" s="11"/>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K85" s="11"/>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="4">
         <v>82</v>
       </c>
@@ -2648,15 +3020,18 @@
       <c r="E86" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G86" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G86" s="11"/>
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
       <c r="J86" s="11"/>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K86" s="11"/>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" s="4">
         <v>83</v>
       </c>
@@ -2670,13 +3045,16 @@
       <c r="E87" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F87" s="11"/>
+      <c r="F87" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
       <c r="I87" s="11"/>
       <c r="J87" s="11"/>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K87" s="11"/>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" s="4">
         <v>84</v>
       </c>
@@ -2690,13 +3068,16 @@
       <c r="E88" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F88" s="11"/>
+      <c r="F88" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
       <c r="J88" s="11"/>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K88" s="11"/>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" s="4">
         <v>85</v>
       </c>
@@ -2710,15 +3091,18 @@
       <c r="E89" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G89" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G89" s="11"/>
       <c r="H89" s="11"/>
       <c r="I89" s="11"/>
       <c r="J89" s="11"/>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K89" s="11"/>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" s="4">
         <v>86</v>
       </c>
@@ -2732,15 +3116,18 @@
       <c r="E90" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G90" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
       <c r="J90" s="11"/>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K90" s="11"/>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" s="4">
         <v>87</v>
       </c>
@@ -2754,13 +3141,16 @@
       <c r="E91" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F91" s="11"/>
+      <c r="F91" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
       <c r="J91" s="11"/>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K91" s="11"/>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" s="4">
         <v>88</v>
       </c>
@@ -2774,13 +3164,16 @@
       <c r="E92" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F92" s="11"/>
+      <c r="F92" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
       <c r="I92" s="11"/>
       <c r="J92" s="11"/>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K92" s="11"/>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" s="4">
         <v>89</v>
       </c>
@@ -2794,13 +3187,16 @@
       <c r="E93" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F93" s="11"/>
+      <c r="F93" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
       <c r="J93" s="11"/>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K93" s="11"/>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" s="4">
         <v>90</v>
       </c>
@@ -2814,13 +3210,16 @@
       <c r="E94" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F94" s="11"/>
+      <c r="F94" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
       <c r="J94" s="11"/>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K94" s="11"/>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" s="4">
         <v>91</v>
       </c>
@@ -2834,15 +3233,18 @@
       <c r="E95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G95" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G95" s="11"/>
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
       <c r="J95" s="11"/>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K95" s="11"/>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" s="4">
         <v>92</v>
       </c>
@@ -2856,13 +3258,16 @@
       <c r="E96" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F96" s="11"/>
+      <c r="F96" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
       <c r="J96" s="11"/>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K96" s="11"/>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="4">
         <v>93</v>
       </c>
@@ -2876,13 +3281,16 @@
       <c r="E97" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F97" s="11"/>
+      <c r="F97" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
       <c r="J97" s="11"/>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K97" s="11"/>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" s="4">
         <v>94</v>
       </c>
@@ -2896,17 +3304,20 @@
       <c r="E98" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F98" s="11" t="s">
+      <c r="F98" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G98" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G98" s="11" t="s">
+      <c r="H98" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H98" s="11"/>
       <c r="I98" s="11"/>
       <c r="J98" s="11"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K98" s="11"/>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" s="4">
         <v>95</v>
       </c>
@@ -2920,17 +3331,20 @@
       <c r="E99" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="F99" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G99" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G99" s="11" t="s">
+      <c r="H99" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H99" s="11"/>
       <c r="I99" s="11"/>
       <c r="J99" s="11"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K99" s="11"/>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" s="4">
         <v>96</v>
       </c>
@@ -2944,15 +3358,18 @@
       <c r="E100" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F100" s="11" t="s">
+      <c r="F100" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G100" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G100" s="11"/>
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
       <c r="J100" s="11"/>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K100" s="11"/>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="4">
         <v>97</v>
       </c>
@@ -2966,17 +3383,20 @@
       <c r="E101" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F101" s="11" t="s">
+      <c r="F101" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G101" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G101" s="11" t="s">
+      <c r="H101" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H101" s="11"/>
       <c r="I101" s="11"/>
       <c r="J101" s="11"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K101" s="11"/>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" s="4">
         <v>98</v>
       </c>
@@ -2990,15 +3410,18 @@
       <c r="E102" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F102" s="11" t="s">
+      <c r="F102" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G102" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G102" s="11"/>
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
       <c r="J102" s="11"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K102" s="11"/>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="4">
         <v>99</v>
       </c>
@@ -3012,13 +3435,16 @@
       <c r="E103" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F103" s="11"/>
+      <c r="F103" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
       <c r="J103" s="11"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K103" s="11"/>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" s="4">
         <v>100</v>
       </c>
@@ -3032,13 +3458,16 @@
       <c r="E104" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F104" s="11"/>
+      <c r="F104" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
       <c r="J104" s="11"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K104" s="11"/>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="4">
         <v>101</v>
       </c>
@@ -3052,13 +3481,16 @@
       <c r="E105" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F105" s="11"/>
+      <c r="F105" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
       <c r="J105" s="11"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K105" s="11"/>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" s="4">
         <v>102</v>
       </c>
@@ -3072,13 +3504,16 @@
       <c r="E106" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F106" s="11"/>
+      <c r="F106" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K106" s="11"/>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" s="4">
         <v>103</v>
       </c>
@@ -3092,15 +3527,18 @@
       <c r="E107" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F107" s="11" t="s">
+      <c r="F107" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G107" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G107" s="11"/>
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
       <c r="J107" s="11"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K107" s="11"/>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" s="4">
         <v>104</v>
       </c>
@@ -3114,13 +3552,16 @@
       <c r="E108" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F108" s="11"/>
+      <c r="F108" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K108" s="11"/>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" s="4">
         <v>105</v>
       </c>
@@ -3134,13 +3575,16 @@
       <c r="E109" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F109" s="11"/>
+      <c r="F109" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K109" s="11"/>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" s="4">
         <v>2244</v>
       </c>
@@ -3154,15 +3598,15 @@
       <c r="E110" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F110" s="11" t="s">
+      <c r="G110" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G110" s="11"/>
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
       <c r="J110" s="11"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K110" s="11"/>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" s="4">
         <v>2245</v>
       </c>
@@ -3176,15 +3620,15 @@
       <c r="E111" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F111" s="11" t="s">
+      <c r="G111" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G111" s="11"/>
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
       <c r="J111" s="11"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K111" s="11"/>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" s="4">
         <v>2246</v>
       </c>
@@ -3198,15 +3642,15 @@
       <c r="E112" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F112" s="11" t="s">
+      <c r="G112" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="11"/>
       <c r="J112" s="11"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K112" s="11"/>
+    </row>
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" s="4">
         <v>2247</v>
       </c>
@@ -3220,15 +3664,15 @@
       <c r="E113" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F113" s="11" t="s">
+      <c r="G113" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G113" s="11"/>
       <c r="H113" s="11"/>
       <c r="I113" s="11"/>
       <c r="J113" s="11"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K113" s="11"/>
+    </row>
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" s="4">
         <v>2248</v>
       </c>
@@ -3242,15 +3686,15 @@
       <c r="E114" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F114" s="11" t="s">
+      <c r="G114" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G114" s="11"/>
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
       <c r="J114" s="11"/>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="K114" s="11"/>
+    </row>
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" s="2">
         <v>2656</v>
       </c>
@@ -3265,7 +3709,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" s="2">
         <v>2658</v>
       </c>
@@ -3280,7 +3724,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" s="2">
         <v>2660</v>
       </c>
@@ -3295,7 +3739,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" s="2">
         <v>2662</v>
       </c>
@@ -3310,7 +3754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" s="2">
         <v>2664</v>
       </c>
@@ -3325,7 +3769,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" s="2">
         <v>2665</v>
       </c>
@@ -3340,7 +3784,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" s="2">
         <v>2666</v>
       </c>
@@ -3355,7 +3799,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" s="2">
         <v>2667</v>
       </c>
@@ -3370,7 +3814,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" s="2">
         <v>2670</v>
       </c>
@@ -3385,7 +3829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" s="2">
         <v>2672</v>
       </c>
@@ -3400,7 +3844,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" s="2">
         <v>2674</v>
       </c>
@@ -3415,7 +3859,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" s="2">
         <v>2676</v>
       </c>
@@ -3430,7 +3874,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" s="2">
         <v>2678</v>
       </c>
@@ -3445,7 +3889,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" s="2">
         <v>2679</v>
       </c>
@@ -3460,7 +3904,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B129" s="2">
         <v>2680</v>
       </c>
@@ -3475,7 +3919,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" s="2">
         <v>2681</v>
       </c>
@@ -3490,7 +3934,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" s="2">
         <v>2684</v>
       </c>
@@ -3505,7 +3949,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B132" s="2">
         <v>2686</v>
       </c>
@@ -3520,7 +3964,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" s="2">
         <v>2688</v>
       </c>
@@ -3535,7 +3979,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" s="2">
         <v>2690</v>
       </c>
@@ -3550,7 +3994,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" s="2">
         <v>2692</v>
       </c>
@@ -3565,7 +4009,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" s="2">
         <v>2693</v>
       </c>
@@ -3580,7 +4024,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" s="2">
         <v>2694</v>
       </c>
@@ -3595,7 +4039,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B138" s="2">
         <v>2695</v>
       </c>
@@ -3610,7 +4054,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B139" s="2">
         <v>2698</v>
       </c>
@@ -3625,7 +4069,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B140" s="2">
         <v>2700</v>
       </c>
@@ -3640,7 +4084,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B141" s="2">
         <v>2702</v>
       </c>
@@ -3655,7 +4099,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B142" s="2">
         <v>2704</v>
       </c>
@@ -3670,7 +4114,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" s="2">
         <v>2706</v>
       </c>
@@ -3685,7 +4129,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" s="2">
         <v>2707</v>
       </c>
@@ -3700,7 +4144,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" s="2">
         <v>2708</v>
       </c>
@@ -3715,7 +4159,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" s="2">
         <v>2709</v>
       </c>
@@ -3730,7 +4174,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" s="2">
         <v>2712</v>
       </c>
@@ -3745,7 +4189,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B148" s="2">
         <v>2714</v>
       </c>
@@ -3760,7 +4204,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" s="2">
         <v>2716</v>
       </c>
@@ -3775,7 +4219,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B150" s="2">
         <v>2718</v>
       </c>
@@ -3790,7 +4234,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" s="2">
         <v>2720</v>
       </c>
@@ -3805,7 +4249,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" s="2">
         <v>2721</v>
       </c>
@@ -3820,7 +4264,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" s="2">
         <v>2722</v>
       </c>
@@ -3835,7 +4279,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" s="2">
         <v>2723</v>
       </c>
@@ -3850,7 +4294,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B155" s="2">
         <v>2726</v>
       </c>
@@ -3865,7 +4309,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B156" s="2">
         <v>2728</v>
       </c>
@@ -3880,7 +4324,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B157" s="2">
         <v>2730</v>
       </c>
@@ -3895,7 +4339,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" s="2">
         <v>2732</v>
       </c>
@@ -3910,7 +4354,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" s="2">
         <v>2734</v>
       </c>
@@ -3925,7 +4369,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B160" s="2">
         <v>2735</v>
       </c>
@@ -3940,7 +4384,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B161" s="2">
         <v>2736</v>
       </c>
@@ -3955,7 +4399,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" s="2">
         <v>2737</v>
       </c>
@@ -3970,7 +4414,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B163" s="2">
         <v>2740</v>
       </c>
@@ -3985,7 +4429,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B164" s="2">
         <v>2742</v>
       </c>
@@ -4000,7 +4444,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B165" s="2">
         <v>2744</v>
       </c>
@@ -4015,7 +4459,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B166" s="2">
         <v>2746</v>
       </c>
@@ -4030,7 +4474,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B167" s="2">
         <v>2748</v>
       </c>
@@ -4045,7 +4489,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" s="2">
         <v>2749</v>
       </c>
@@ -4060,7 +4504,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B169" s="2">
         <v>2750</v>
       </c>
@@ -4075,7 +4519,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B170" s="2">
         <v>2751</v>
       </c>
@@ -4090,7 +4534,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B171" s="2">
         <v>2754</v>
       </c>
@@ -4105,7 +4549,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B172" s="2">
         <v>2756</v>
       </c>
@@ -4120,7 +4564,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B173" s="2">
         <v>2758</v>
       </c>
@@ -4135,7 +4579,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B174" s="2">
         <v>2760</v>
       </c>
@@ -4150,7 +4594,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B175" s="2">
         <v>2762</v>
       </c>
@@ -4165,7 +4609,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B176" s="2">
         <v>2763</v>
       </c>
@@ -4180,7 +4624,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B177" s="2">
         <v>2764</v>
       </c>
@@ -4195,7 +4639,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B178" s="2">
         <v>2765</v>
       </c>
@@ -4210,7 +4654,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B179" s="2">
         <v>2768</v>
       </c>
@@ -4225,7 +4669,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B180" s="2">
         <v>2770</v>
       </c>
@@ -4240,7 +4684,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B181" s="2">
         <v>2772</v>
       </c>
@@ -4255,7 +4699,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B182" s="2">
         <v>2774</v>
       </c>
@@ -4270,7 +4714,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B183" s="2">
         <v>2776</v>
       </c>
@@ -4285,7 +4729,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B184" s="2">
         <v>2777</v>
       </c>
@@ -4300,7 +4744,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B185" s="2">
         <v>2778</v>
       </c>
@@ -4315,7 +4759,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B186" s="2">
         <v>2779</v>
       </c>
@@ -4330,7 +4774,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B187" s="2">
         <v>2782</v>
       </c>
@@ -4345,7 +4789,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B188" s="2">
         <v>2784</v>
       </c>
@@ -4360,7 +4804,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B189" s="2">
         <v>2786</v>
       </c>
@@ -4375,7 +4819,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B190" s="2">
         <v>2788</v>
       </c>
@@ -4390,7 +4834,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B191" s="2">
         <v>2790</v>
       </c>
@@ -4405,7 +4849,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B192" s="2">
         <v>2791</v>
       </c>
@@ -4420,7 +4864,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B193" s="2">
         <v>2792</v>
       </c>
@@ -4435,7 +4879,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B194" s="2">
         <v>2793</v>
       </c>
@@ -4450,7 +4894,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B195" s="2">
         <v>2796</v>
       </c>
@@ -4465,7 +4909,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B196" s="2">
         <v>2798</v>
       </c>
@@ -4480,7 +4924,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B197" s="2">
         <v>2800</v>
       </c>
@@ -4495,7 +4939,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B198" s="2">
         <v>2802</v>
       </c>
@@ -4510,7 +4954,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B199" s="2">
         <v>2804</v>
       </c>
@@ -4525,7 +4969,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B200" s="2">
         <v>2805</v>
       </c>
@@ -4540,7 +4984,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B201" s="2">
         <v>2806</v>
       </c>
@@ -4555,7 +4999,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B202" s="2">
         <v>2807</v>
       </c>
@@ -4570,7 +5014,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B203" s="2">
         <v>2810</v>
       </c>
@@ -4585,7 +5029,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B204" s="2">
         <v>2812</v>
       </c>
@@ -4600,7 +5044,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B205" s="2">
         <v>2814</v>
       </c>
@@ -4615,7 +5059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B206" s="2">
         <v>2816</v>
       </c>
@@ -4630,7 +5074,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B207" s="2">
         <v>2818</v>
       </c>
@@ -4645,7 +5089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B208" s="2">
         <v>2819</v>
       </c>
@@ -4660,7 +5104,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B209" s="2">
         <v>2820</v>
       </c>
@@ -4675,7 +5119,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B210" s="2">
         <v>2821</v>
       </c>
@@ -4690,7 +5134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B211" s="2">
         <v>2824</v>
       </c>
@@ -4705,7 +5149,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B212" s="2">
         <v>2826</v>
       </c>
@@ -4720,7 +5164,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B213" s="2">
         <v>2828</v>
       </c>
@@ -4735,7 +5179,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B214" s="2">
         <v>2830</v>
       </c>
@@ -4750,7 +5194,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B215" s="2">
         <v>2832</v>
       </c>
@@ -4765,7 +5209,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B216" s="2">
         <v>2833</v>
       </c>
@@ -4780,7 +5224,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B217" s="2">
         <v>2834</v>
       </c>
@@ -4795,7 +5239,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B218" s="2">
         <v>2835</v>
       </c>
@@ -4810,7 +5254,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B219" s="2">
         <v>2838</v>
       </c>
@@ -4825,7 +5269,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B220" s="2">
         <v>2840</v>
       </c>
@@ -4840,7 +5284,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B221" s="2">
         <v>2842</v>
       </c>
@@ -4855,7 +5299,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B222" s="2">
         <v>2844</v>
       </c>
@@ -4870,7 +5314,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B223" s="2">
         <v>2846</v>
       </c>
@@ -4885,7 +5329,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B224" s="2">
         <v>2847</v>
       </c>
@@ -4900,7 +5344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B225" s="2">
         <v>2848</v>
       </c>
@@ -4915,7 +5359,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B226" s="2">
         <v>2849</v>
       </c>
@@ -4930,7 +5374,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B227" s="2">
         <v>2852</v>
       </c>
@@ -4945,7 +5389,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" s="2">
         <v>2854</v>
       </c>
@@ -4960,7 +5404,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B229" s="2">
         <v>2856</v>
       </c>
@@ -4975,7 +5419,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B230" s="2">
         <v>2858</v>
       </c>
@@ -4990,7 +5434,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B231" s="2">
         <v>2860</v>
       </c>
@@ -5005,7 +5449,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B232" s="2">
         <v>2861</v>
       </c>
@@ -5020,7 +5464,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B233" s="2">
         <v>2862</v>
       </c>
@@ -5035,7 +5479,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B234" s="2">
         <v>2863</v>
       </c>
@@ -5050,7 +5494,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B235" s="2">
         <v>2866</v>
       </c>
@@ -5065,7 +5509,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B236" s="2">
         <v>2868</v>
       </c>
@@ -5080,7 +5524,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" s="2">
         <v>2870</v>
       </c>
@@ -5095,7 +5539,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B238" s="2">
         <v>2872</v>
       </c>
@@ -5110,7 +5554,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B239" s="2">
         <v>2874</v>
       </c>
@@ -5125,7 +5569,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B240" s="2">
         <v>2875</v>
       </c>
@@ -5140,7 +5584,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B241" s="2">
         <v>2876</v>
       </c>
@@ -5155,7 +5599,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B242" s="2">
         <v>2877</v>
       </c>
@@ -5170,7 +5614,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B243" s="2">
         <v>2880</v>
       </c>
@@ -5185,7 +5629,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B244" s="2">
         <v>2882</v>
       </c>
@@ -5200,7 +5644,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B245" s="2">
         <v>2884</v>
       </c>
@@ -5215,7 +5659,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B246" s="2">
         <v>2886</v>
       </c>
@@ -5230,7 +5674,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B247" s="2">
         <v>2888</v>
       </c>
@@ -5245,7 +5689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B248" s="2">
         <v>2889</v>
       </c>
@@ -5260,7 +5704,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B249" s="2">
         <v>2890</v>
       </c>
@@ -5275,7 +5719,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B250" s="2">
         <v>2891</v>
       </c>
@@ -5290,7 +5734,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B251" s="2">
         <v>2894</v>
       </c>
@@ -5305,7 +5749,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B252" s="2">
         <v>2896</v>
       </c>
@@ -5320,7 +5764,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B253" s="2">
         <v>2898</v>
       </c>
@@ -5335,7 +5779,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B254" s="2">
         <v>2900</v>
       </c>
@@ -5350,7 +5794,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B255" s="2">
         <v>2902</v>
       </c>
@@ -5365,7 +5809,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B256" s="2">
         <v>2903</v>
       </c>
@@ -5380,7 +5824,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B257" s="2">
         <v>2904</v>
       </c>
@@ -5395,7 +5839,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B258" s="2">
         <v>2905</v>
       </c>
@@ -5410,7 +5854,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B259" s="2">
         <v>2908</v>
       </c>
@@ -5425,7 +5869,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B260" s="2">
         <v>2910</v>
       </c>
@@ -5440,7 +5884,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B261" s="2">
         <v>2912</v>
       </c>
@@ -5455,7 +5899,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B262" s="2">
         <v>2914</v>
       </c>
@@ -5470,7 +5914,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B263" s="2">
         <v>2916</v>
       </c>
@@ -5485,7 +5929,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B264" s="2">
         <v>2917</v>
       </c>
@@ -5500,7 +5944,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B265" s="2">
         <v>2918</v>
       </c>
@@ -5515,7 +5959,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B266" s="2">
         <v>2919</v>
       </c>
@@ -5530,7 +5974,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B267" s="2">
         <v>2922</v>
       </c>
@@ -5545,7 +5989,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B268" s="2">
         <v>2924</v>
       </c>
@@ -5560,7 +6004,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B269" s="2">
         <v>2926</v>
       </c>
@@ -5575,7 +6019,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B270" s="2">
         <v>2928</v>
       </c>
@@ -5590,7 +6034,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B271" s="2">
         <v>2930</v>
       </c>
@@ -5605,7 +6049,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B272" s="2">
         <v>2931</v>
       </c>
@@ -5620,7 +6064,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B273" s="2">
         <v>2932</v>
       </c>
@@ -5635,7 +6079,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B274" s="2">
         <v>2933</v>
       </c>
@@ -5650,7 +6094,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B275" s="2">
         <v>2936</v>
       </c>
@@ -5665,7 +6109,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B276" s="2">
         <v>2938</v>
       </c>
@@ -5680,7 +6124,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B277" s="2">
         <v>2940</v>
       </c>
@@ -5695,7 +6139,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B278" s="2">
         <v>2942</v>
       </c>
@@ -5710,7 +6154,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B279" s="2">
         <v>2944</v>
       </c>
@@ -5725,7 +6169,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B280" s="2">
         <v>2945</v>
       </c>
@@ -5740,7 +6184,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B281" s="2">
         <v>2946</v>
       </c>
@@ -5755,7 +6199,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B282" s="2">
         <v>2947</v>
       </c>
@@ -5770,7 +6214,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B283" s="2">
         <v>2950</v>
       </c>
@@ -5785,7 +6229,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B284" s="2">
         <v>2952</v>
       </c>
@@ -5800,7 +6244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B285" s="2">
         <v>2954</v>
       </c>
@@ -5815,7 +6259,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B286" s="2">
         <v>2956</v>
       </c>
@@ -5830,7 +6274,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B287" s="2">
         <v>2958</v>
       </c>
@@ -5845,7 +6289,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B288" s="2">
         <v>2959</v>
       </c>
@@ -5860,7 +6304,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" s="2">
         <v>2960</v>
       </c>
@@ -5875,7 +6319,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" s="2">
         <v>2961</v>
       </c>
@@ -5890,7 +6334,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" s="2">
         <v>2964</v>
       </c>
@@ -5905,7 +6349,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" s="2">
         <v>2966</v>
       </c>
@@ -5920,7 +6364,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B293" s="2">
         <v>2968</v>
       </c>
@@ -5935,7 +6379,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" s="2">
         <v>2970</v>
       </c>
@@ -5950,7 +6394,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" s="2">
         <v>2972</v>
       </c>
@@ -5965,7 +6409,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" s="2">
         <v>2973</v>
       </c>
@@ -5980,7 +6424,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" s="2">
         <v>2974</v>
       </c>
@@ -5995,7 +6439,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" s="2">
         <v>2975</v>
       </c>
@@ -6010,7 +6454,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B299" s="2">
         <v>2992</v>
       </c>
@@ -6025,7 +6469,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" s="2">
         <v>2994</v>
       </c>
@@ -6040,7 +6484,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" s="2">
         <v>2996</v>
       </c>
@@ -6055,7 +6499,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" s="2">
         <v>2998</v>
       </c>
@@ -6070,7 +6514,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" s="2">
         <v>3000</v>
       </c>
@@ -6085,7 +6529,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" s="2">
         <v>3001</v>
       </c>
@@ -6100,7 +6544,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" s="2">
         <v>3002</v>
       </c>
@@ -6115,7 +6559,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" s="2">
         <v>3003</v>
       </c>
@@ -6130,7 +6574,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" s="2">
         <v>3020</v>
       </c>
@@ -6145,7 +6589,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" s="2">
         <v>3022</v>
       </c>
@@ -6160,7 +6604,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" s="2">
         <v>3024</v>
       </c>
@@ -6175,7 +6619,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" s="2">
         <v>3026</v>
       </c>
@@ -6190,7 +6634,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" s="2">
         <v>3028</v>
       </c>
@@ -6205,7 +6649,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" s="2">
         <v>3029</v>
       </c>
@@ -6220,7 +6664,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" s="2">
         <v>3030</v>
       </c>
@@ -6235,7 +6679,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" s="2">
         <v>3031</v>
       </c>
@@ -6250,7 +6694,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" s="2">
         <v>3034</v>
       </c>
@@ -6265,7 +6709,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" s="2">
         <v>3036</v>
       </c>
@@ -6280,7 +6724,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" s="2">
         <v>3038</v>
       </c>
@@ -6295,7 +6739,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" s="2">
         <v>3040</v>
       </c>
@@ -6310,7 +6754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" s="2">
         <v>3042</v>
       </c>
@@ -6325,7 +6769,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" s="2">
         <v>3043</v>
       </c>
@@ -6340,7 +6784,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" s="2">
         <v>3044</v>
       </c>
@@ -6355,7 +6799,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" s="2">
         <v>3045</v>
       </c>
@@ -6370,7 +6814,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" s="2">
         <v>3048</v>
       </c>
@@ -6385,7 +6829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" s="2">
         <v>3050</v>
       </c>
@@ -6400,7 +6844,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" s="2">
         <v>3052</v>
       </c>
@@ -6415,7 +6859,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" s="2">
         <v>3054</v>
       </c>
@@ -6430,7 +6874,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" s="2">
         <v>3056</v>
       </c>
@@ -6445,7 +6889,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328" s="2">
         <v>3057</v>
       </c>
@@ -6460,7 +6904,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329" s="2">
         <v>3058</v>
       </c>
@@ -6475,7 +6919,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" s="2">
         <v>3059</v>
       </c>
@@ -6490,7 +6934,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" s="2">
         <v>3062</v>
       </c>
@@ -6505,7 +6949,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" s="2">
         <v>3064</v>
       </c>
@@ -6520,7 +6964,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" s="2">
         <v>3066</v>
       </c>
@@ -6535,7 +6979,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" s="2">
         <v>3068</v>
       </c>
@@ -6550,7 +6994,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" s="2">
         <v>3070</v>
       </c>
@@ -6565,7 +7009,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336" s="2">
         <v>3071</v>
       </c>
@@ -6580,7 +7024,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B337" s="2">
         <v>3072</v>
       </c>
@@ -6595,7 +7039,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B338" s="2">
         <v>3073</v>
       </c>
@@ -6610,7 +7054,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="339" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B339" s="2">
         <v>3076</v>
       </c>
@@ -6625,7 +7069,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="340" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B340" s="2">
         <v>3078</v>
       </c>
@@ -6640,7 +7084,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="341" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B341" s="2">
         <v>3080</v>
       </c>
@@ -6655,7 +7099,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="342" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B342" s="2">
         <v>3082</v>
       </c>
@@ -6670,7 +7114,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="343" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B343" s="2">
         <v>3084</v>
       </c>
@@ -6685,7 +7129,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="344" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B344" s="2">
         <v>3085</v>
       </c>
@@ -6700,7 +7144,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="345" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B345" s="2">
         <v>3086</v>
       </c>
@@ -6715,7 +7159,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="346" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B346" s="2">
         <v>3087</v>
       </c>
@@ -6730,7 +7174,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="347" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B347" s="2">
         <v>3090</v>
       </c>
@@ -6745,7 +7189,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="348" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B348" s="2">
         <v>3092</v>
       </c>
@@ -6760,7 +7204,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="349" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B349" s="2">
         <v>3094</v>
       </c>
@@ -6775,7 +7219,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="350" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B350" s="2">
         <v>3096</v>
       </c>
@@ -6790,7 +7234,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="351" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B351" s="2">
         <v>3098</v>
       </c>
@@ -6805,7 +7249,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="352" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B352" s="2">
         <v>3099</v>
       </c>
@@ -6820,7 +7264,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="353" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B353" s="2">
         <v>3100</v>
       </c>
@@ -6835,7 +7279,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="354" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B354" s="2">
         <v>3101</v>
       </c>
@@ -6850,7 +7294,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="355" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B355" s="2">
         <v>3104</v>
       </c>
@@ -6865,7 +7309,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="356" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B356" s="2">
         <v>3106</v>
       </c>
@@ -6880,7 +7324,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="357" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B357" s="2">
         <v>3108</v>
       </c>
@@ -6895,7 +7339,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="358" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B358" s="2">
         <v>3110</v>
       </c>
@@ -6910,7 +7354,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="359" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B359" s="2">
         <v>3112</v>
       </c>
@@ -6925,7 +7369,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="360" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B360" s="2">
         <v>3113</v>
       </c>
@@ -6940,7 +7384,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="361" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B361" s="2">
         <v>3114</v>
       </c>
@@ -6955,7 +7399,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="362" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B362" s="2">
         <v>3115</v>
       </c>
@@ -6970,7 +7414,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="363" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B363" s="2">
         <v>3118</v>
       </c>
@@ -6985,7 +7429,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="364" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B364" s="2">
         <v>3120</v>
       </c>
@@ -7000,7 +7444,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="365" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B365" s="2">
         <v>3122</v>
       </c>
@@ -7015,7 +7459,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="366" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B366" s="2">
         <v>3124</v>
       </c>
@@ -7030,7 +7474,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="367" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B367" s="2">
         <v>3126</v>
       </c>
@@ -7045,7 +7489,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="368" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B368" s="2">
         <v>3127</v>
       </c>
@@ -7060,7 +7504,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="369" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B369" s="2">
         <v>3128</v>
       </c>
@@ -7075,7 +7519,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="370" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B370" s="2">
         <v>3129</v>
       </c>
@@ -7090,7 +7534,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="371" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B371" s="2">
         <v>3132</v>
       </c>
@@ -7105,7 +7549,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="372" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B372" s="2">
         <v>3134</v>
       </c>
@@ -7120,7 +7564,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="373" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B373" s="2">
         <v>3136</v>
       </c>
@@ -7135,7 +7579,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="374" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B374" s="2">
         <v>3138</v>
       </c>
@@ -7150,7 +7594,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="375" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B375" s="2">
         <v>3140</v>
       </c>
@@ -7165,7 +7609,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="376" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B376" s="2">
         <v>3141</v>
       </c>
@@ -7180,7 +7624,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="377" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B377" s="2">
         <v>3142</v>
       </c>
@@ -7195,7 +7639,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="378" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B378" s="2">
         <v>3143</v>
       </c>
@@ -7210,7 +7654,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="379" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B379" s="2">
         <v>3146</v>
       </c>
@@ -7225,7 +7669,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="380" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B380" s="2">
         <v>3148</v>
       </c>
@@ -7240,7 +7684,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="381" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B381" s="2">
         <v>3150</v>
       </c>
@@ -7255,7 +7699,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="382" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B382" s="2">
         <v>3152</v>
       </c>
@@ -7270,7 +7714,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="383" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B383" s="2">
         <v>3154</v>
       </c>
@@ -7285,7 +7729,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="384" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B384" s="2">
         <v>3155</v>
       </c>
@@ -7300,7 +7744,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="385" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B385" s="2">
         <v>3156</v>
       </c>
@@ -7315,7 +7759,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="386" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B386" s="2">
         <v>3157</v>
       </c>
@@ -7330,7 +7774,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="387" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B387" s="2">
         <v>3160</v>
       </c>
@@ -7345,7 +7789,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="388" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B388" s="2">
         <v>3162</v>
       </c>
@@ -7360,7 +7804,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="389" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B389" s="2">
         <v>3164</v>
       </c>
@@ -7375,7 +7819,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="390" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B390" s="2">
         <v>3166</v>
       </c>
@@ -7390,7 +7834,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="391" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B391" s="2">
         <v>3168</v>
       </c>
@@ -7405,7 +7849,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="392" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B392" s="2">
         <v>3169</v>
       </c>
@@ -7420,7 +7864,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="393" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B393" s="2">
         <v>3170</v>
       </c>
@@ -7435,7 +7879,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="394" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B394" s="2">
         <v>3171</v>
       </c>
@@ -7450,7 +7894,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="395" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B395" s="2">
         <v>3188</v>
       </c>
@@ -7465,7 +7909,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="396" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B396" s="2">
         <v>3190</v>
       </c>
@@ -7480,7 +7924,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="397" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B397" s="2">
         <v>3192</v>
       </c>
@@ -7495,7 +7939,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="398" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B398" s="2">
         <v>3194</v>
       </c>
@@ -7510,7 +7954,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="399" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B399" s="2">
         <v>3196</v>
       </c>
@@ -7525,7 +7969,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="400" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B400" s="2">
         <v>3197</v>
       </c>
@@ -7540,7 +7984,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="401" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B401" s="2">
         <v>3198</v>
       </c>
@@ -7555,7 +7999,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="402" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B402" s="2">
         <v>3199</v>
       </c>
@@ -7570,7 +8014,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="403" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B403" s="2">
         <v>3202</v>
       </c>
@@ -7585,7 +8029,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="404" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B404" s="2">
         <v>3204</v>
       </c>
@@ -7600,7 +8044,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="405" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B405" s="2">
         <v>3206</v>
       </c>
@@ -7615,7 +8059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="406" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B406" s="2">
         <v>3208</v>
       </c>
@@ -7630,7 +8074,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="407" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B407" s="2">
         <v>3210</v>
       </c>
@@ -7645,7 +8089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="408" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B408" s="2">
         <v>3211</v>
       </c>
@@ -7660,7 +8104,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="409" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B409" s="2">
         <v>3212</v>
       </c>
@@ -7675,7 +8119,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="410" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B410" s="2">
         <v>3213</v>
       </c>
@@ -7690,7 +8134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="411" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B411" s="2">
         <v>3216</v>
       </c>
@@ -7705,7 +8149,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="412" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B412" s="2">
         <v>3218</v>
       </c>
@@ -7720,7 +8164,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="413" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B413" s="2">
         <v>3220</v>
       </c>
@@ -7735,7 +8179,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="414" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B414" s="2">
         <v>3222</v>
       </c>
@@ -7750,7 +8194,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="415" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B415" s="2">
         <v>3224</v>
       </c>
@@ -7765,7 +8209,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="416" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B416" s="2">
         <v>3225</v>
       </c>
@@ -7780,7 +8224,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="417" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B417" s="2">
         <v>3226</v>
       </c>
@@ -7795,7 +8239,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="418" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B418" s="2">
         <v>3227</v>
       </c>
@@ -7810,7 +8254,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="419" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B419" s="2">
         <v>3230</v>
       </c>
@@ -7825,7 +8269,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="420" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B420" s="2">
         <v>3232</v>
       </c>
@@ -7840,7 +8284,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="421" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B421" s="2">
         <v>3234</v>
       </c>
@@ -7855,7 +8299,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="422" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="422" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B422" s="2">
         <v>3236</v>
       </c>
@@ -7870,7 +8314,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="423" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="423" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B423" s="2">
         <v>3238</v>
       </c>
@@ -7885,7 +8329,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="424" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="424" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B424" s="2">
         <v>3239</v>
       </c>
@@ -7900,7 +8344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="425" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="425" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B425" s="2">
         <v>3240</v>
       </c>
@@ -7915,7 +8359,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="426" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="426" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B426" s="2">
         <v>3241</v>
       </c>
@@ -7930,7 +8374,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="427" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="427" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B427" s="2">
         <v>3244</v>
       </c>
@@ -7945,7 +8389,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="428" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="428" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B428" s="2">
         <v>3246</v>
       </c>
@@ -7960,7 +8404,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="429" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="429" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B429" s="2">
         <v>3248</v>
       </c>
@@ -7975,7 +8419,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="430" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="430" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B430" s="2">
         <v>3250</v>
       </c>
@@ -7990,7 +8434,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="431" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="431" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B431" s="2">
         <v>3252</v>
       </c>
@@ -8005,7 +8449,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="432" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="432" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B432" s="2">
         <v>3253</v>
       </c>
@@ -8020,7 +8464,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="433" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="433" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B433" s="2">
         <v>3254</v>
       </c>
@@ -8035,7 +8479,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="434" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="434" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B434" s="2">
         <v>3255</v>
       </c>
@@ -8050,7 +8494,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="435" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="435" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B435" s="2">
         <v>3258</v>
       </c>
@@ -8065,7 +8509,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="436" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="436" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B436" s="2">
         <v>3260</v>
       </c>
@@ -8080,7 +8524,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="437" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="437" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B437" s="2">
         <v>3262</v>
       </c>
@@ -8095,7 +8539,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="438" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="438" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B438" s="2">
         <v>3264</v>
       </c>
@@ -8110,7 +8554,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="439" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="439" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B439" s="2">
         <v>3266</v>
       </c>
@@ -8125,7 +8569,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="440" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="440" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B440" s="2">
         <v>3267</v>
       </c>
@@ -8140,7 +8584,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="441" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="441" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B441" s="2">
         <v>3268</v>
       </c>
@@ -8155,7 +8599,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="442" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="442" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B442" s="2">
         <v>3269</v>
       </c>
@@ -8170,7 +8614,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="443" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="443" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B443" s="2">
         <v>3272</v>
       </c>
@@ -8185,7 +8629,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="444" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="444" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B444" s="2">
         <v>3274</v>
       </c>
@@ -8200,7 +8644,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="445" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="445" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B445" s="2">
         <v>3276</v>
       </c>
@@ -8215,7 +8659,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="446" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="446" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B446" s="2">
         <v>3278</v>
       </c>
@@ -8230,7 +8674,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="447" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="447" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B447" s="2">
         <v>3280</v>
       </c>
@@ -8245,7 +8689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="448" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="448" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B448" s="2">
         <v>3281</v>
       </c>
@@ -8260,7 +8704,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="449" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="449" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B449" s="2">
         <v>3282</v>
       </c>
@@ -8275,7 +8719,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="450" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="450" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B450" s="2">
         <v>3283</v>
       </c>
